--- a/outputs/Block2_Popular_Vote_Dependency_Audit_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Dependency_Audit_v12.xlsx
@@ -37,10 +37,10 @@
     <t>Inputs: EDPP, ERPP; historical DPP/RPP only define targets and Other/error estimates</t>
   </si>
   <si>
-    <t>17 Senate-related national columns perturbed</t>
-  </si>
-  <si>
-    <t>42 targets; 71 predictors</t>
+    <t>3 Senate-related national columns perturbed</t>
+  </si>
+  <si>
+    <t>10 targets; 42 predictors</t>
   </si>
 </sst>
 </file>
